--- a/output/第10期計画_要介護認定データの確認.xlsx
+++ b/output/第10期計画_要介護認定データの確認.xlsx
@@ -2313,10 +2313,8 @@
       <c r="J9" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="K9" s="10" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="K9" s="10" t="n">
+        <v>18.4</v>
       </c>
       <c r="L9" s="10" t="inlineStr"/>
       <c r="M9" s="10" t="inlineStr"/>
@@ -2399,10 +2397,8 @@
       <c r="J11" s="10" t="n">
         <v>12.7</v>
       </c>
-      <c r="K11" s="10" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="K11" s="10" t="n">
+        <v>12.7</v>
       </c>
       <c r="L11" s="10" t="inlineStr"/>
       <c r="M11" s="10" t="inlineStr"/>
@@ -2788,7 +2784,7 @@
     <row r="26" ht="104" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>注1）調整済み認定率には2系列があり、令和7年3月末で【注目する地域のみ】18.4％、【他地域と比較】16.7％と値が異なる。18.4％は当広域連合のみを対象に標準化した値であり、全国・北海道と比較できない。第4章のH01でこの18.4％を撤回し見える化W144に改めた判断は、原典により裏付けられた。他地域と比較する場合は【他地域と比較】系列（16.7％）を用いる。注2）調整済み重度認定率は平成30年3月末5.4％から令和7年3月末4.7％へ一貫して低下している。調整済み軽度認定率は令和5年3月末11.7％を底に令和7年3月末12.0％へ上昇しており、受託者の自己点検の訂正のとおりである。注3）認定率は令和元年3月末20.3％から令和8年3月末21.8％へ1.5ポイント上昇したが、年齢構成を調整すると17.2％（令和元年）から16.7％（令和7年）へ低下している。認定率の上昇は高齢化によるものである。</t>
+          <t>注1）調整済み認定率には2系列があり、令和7年3月末で【注目する地域のみ】18.4％、【他地域と比較】16.7％と値が異なる。令和8年10月19日に受領した【注目する地域のみ】の出力により、当広域連合の値は18.4％の側であることが確かめられた（平成25年3月末から令和7年3月末までの221件が受領値と一致）。【他地域と比較】の系列が、当広域連合の値を別の基準人口で標準化したものか、他の地域の値かは特定できていない（確認事項No.190）。第4章のH01で18.4％を撤回し見える化W144に改めた判断は、いずれであっても全国・北海道と直接は比較できないことによる。注2）2系列の値を混ぜて1つの文に並べない。1つの系列の中での時点の比較は標準化の基準によらず成り立つ。【注目する地域のみ】の調整済み重度認定率は平成25年3月末7.2％から令和8年3月末5.2％へ一貫して低下し、調整済み軽度認定率は令和5年3月末12.8％を底に令和6年3月末13.2％へ上昇した後は横ばいである。【他地域と比較】の系列では重度が平成30年3月末5.4％から令和7年3月末4.7％へ低下し、軽度が令和5年3月末11.7％を底に令和7年3月末12.0％へ上昇している。注3）認定率は令和元年3月末20.3％から令和8年3月末21.8％へ1.5ポイント上昇したが、【注目する地域のみ】の調整済み認定率は19.1％（令和元年3月末）から18.4％（令和8年3月末）へ低下している。認定率の上昇は高齢化によるものである。</t>
         </is>
       </c>
     </row>
